--- a/aggregator/documentation/links.xlsx
+++ b/aggregator/documentation/links.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10322"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/pushkarchauhan91/Documents/workspace/parent/aggregator/documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\PCHAUH21\work\workspace_lab\parent\aggregator\documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FDE1CF8-0A52-5445-B6A3-5F913761F284}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B6F4BE5-E822-49B0-9AEC-D90E0E0BAE8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3780" yWindow="1080" windowWidth="28040" windowHeight="17180" activeTab="1" xr2:uid="{0B1A7EAF-F057-DA43-849F-8C9C7ABA47AB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="34776" windowHeight="21096" xr2:uid="{0B1A7EAF-F057-DA43-849F-8C9C7ABA47AB}"/>
   </bookViews>
   <sheets>
     <sheet name="links" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="71">
   <si>
     <t>https://www.youtube.com/@Javatechie/videos</t>
   </si>
@@ -255,6 +255,12 @@
   </si>
   <si>
     <t>SAML vs OpenID Connect</t>
+  </si>
+  <si>
+    <t>https://refactoring.guru/</t>
+  </si>
+  <si>
+    <t>Design Patterns</t>
   </si>
 </sst>
 </file>
@@ -640,25 +646,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{637E73AB-3099-0745-9D11-DBAA2A63EF31}">
-  <dimension ref="A1:A3"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="51.83203125" customWidth="1"/>
+    <col min="1" max="1" width="51.796875" customWidth="1"/>
+    <col min="2" max="2" width="30.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B5" t="s">
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -666,6 +681,7 @@
     <hyperlink ref="A1" r:id="rId1" xr:uid="{D043CDDB-5517-7041-9780-7B66BEDD848E}"/>
     <hyperlink ref="A2" r:id="rId2" xr:uid="{C0931E14-B596-DA48-B53B-7FDB10BD5468}"/>
     <hyperlink ref="A3" r:id="rId3" xr:uid="{568B5860-5A33-894B-A5F5-03F9957E966E}"/>
+    <hyperlink ref="A5" r:id="rId4" xr:uid="{4464D912-28A9-4ECA-9C86-AC5F4777BF36}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -674,14 +690,14 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB0B95AD-0C49-394C-B8C6-94411BE1E023}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="26.33203125" customWidth="1"/>
-    <col min="2" max="2" width="91.33203125" customWidth="1"/>
+    <col min="1" max="1" width="26.296875" customWidth="1"/>
+    <col min="2" max="2" width="91.296875" customWidth="1"/>
     <col min="3" max="3" width="73" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>2</v>
       </c>
@@ -689,7 +705,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -697,7 +713,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>24</v>
       </c>
@@ -708,27 +724,27 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>68</v>
       </c>
@@ -741,19 +757,19 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{344FC21E-3490-FA48-AB53-EC8A6E6A16A5}">
   <dimension ref="A1:D14"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="45.83203125" customWidth="1"/>
-    <col min="3" max="3" width="77.1640625" customWidth="1"/>
+    <col min="2" max="2" width="45.796875" customWidth="1"/>
+    <col min="3" max="3" width="77.19921875" customWidth="1"/>
     <col min="4" max="4" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="51" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -767,7 +783,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -778,7 +794,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -786,7 +802,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
@@ -794,7 +810,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
@@ -802,7 +818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -810,12 +826,12 @@
         <v>21</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:4" ht="34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -826,7 +842,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>32</v>
       </c>
@@ -834,7 +850,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -842,17 +858,17 @@
         <v>31</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
         <v>45</v>
       </c>
@@ -868,13 +884,13 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BEBA27A-683D-3C41-943A-34657167B657}">
   <dimension ref="A1:E20"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.19921875" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="55" customWidth="1"/>
-    <col min="2" max="2" width="56.33203125" customWidth="1"/>
+    <col min="2" max="2" width="56.296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>34</v>
       </c>
@@ -882,17 +898,17 @@
         <v>57</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="34" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="31.2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -900,17 +916,17 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -918,17 +934,17 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>44</v>
       </c>
@@ -936,12 +952,12 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -955,12 +971,12 @@
         <v>59</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>50</v>
       </c>
@@ -974,7 +990,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>52</v>
       </c>
@@ -982,7 +998,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>54</v>
       </c>
@@ -993,12 +1009,12 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>30</v>
       </c>
@@ -1009,7 +1025,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>65</v>
       </c>
@@ -1017,7 +1033,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>67</v>
       </c>
